--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2076,906 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M01</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>睿创微纳</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>（688002）</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>177.58</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>177580</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>人工采纳 09-13《明日买入建议》★核心1：全市场 5558 只筛选、双源校验后综合排序第 1 名。</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>估值与盈利指标取东财快照/F10 口径（见 data/fin 与仪表盘标的明细）</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-14 收盘：现价177.89，MA20=172.09，MA60=157.29，RSI14=69.1，技术面评分46。</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3885.33(-0.07%)；深证成指 13384.57(-0.64%)；沪深300 4480.08(-0.67%)；科创50 1528.27(-1.62%)。09-14 为普跌日，本次买入为逆势加仓。</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>本批 5 笔合计 66.21 万元，使组合现金占比由 21.78% 降至约 8.28%，跌破策略现金下限 20%；且买入当日为普跌日，属逆势加仓，须严格执行个股止损纪律（-8% 或跌破 MA20）。</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：RED；交易后现金占比8%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>是（09-13 DeepSeek 收盘复盘 + 09-13《明日买入建议》全市场筛选）</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>采纳（A/C/D 为 09-13 建议名单内标的）</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交）</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M02</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>星网锐捷</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>（002396）</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>35.87</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>358700</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>人工主动建仓（不在 09-13 建议名单内）：星网锐捷属当日资金流入的通信设备方向，人工判断延续性。</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>估值与盈利指标取东财快照/F10 口径（见 data/fin 与仪表盘标的明细）</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-14 收盘：现价34.82，MA20=35.11，MA60=29.75，RSI14=60.3，技术面评分56。</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3885.33(-0.07%)；深证成指 13384.57(-0.64%)；沪深300 4480.08(-0.67%)；科创50 1528.27(-1.62%)。09-14 为普跌日，本次买入为逆势加仓。</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>本批 5 笔合计 66.21 万元，使组合现金占比由 21.78% 降至约 8.28%，跌破策略现金下限 20%；且买入当日为普跌日，属逆势加仓，须严格执行个股止损纪律（-8% 或跌破 MA20）。</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：RED；交易后现金占比8%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>是（09-13 DeepSeek 收盘复盘 + 09-13《明日买入建议》全市场筛选）</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>部分采纳（标的不在建议名单内，属人工主动决策）</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交）</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M03</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>招商轮船</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>（601872）</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>20.76</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>20760</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>人工采纳 09-13《明日买入建议》○价值5：候选池预筛第 5 名，航运港口方向、低估值（PE14.9）。</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>估值与盈利指标取东财快照/F10 口径（见 data/fin 与仪表盘标的明细）</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-14 收盘：现价20.0，MA20=19.07，MA60=17.52，RSI14=57.7，技术面评分67。</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3885.33(-0.07%)；深证成指 13384.57(-0.64%)；沪深300 4480.08(-0.67%)；科创50 1528.27(-1.62%)。09-14 为普跌日，本次买入为逆势加仓。</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>本批 5 笔合计 66.21 万元，使组合现金占比由 21.78% 降至约 8.28%，跌破策略现金下限 20%；且买入当日为普跌日，属逆势加仓，须严格执行个股止损纪律（-8% 或跌破 MA20）。</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：RED；交易后现金占比8%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>是（09-13 DeepSeek 收盘复盘 + 09-13《明日买入建议》全市场筛选）</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>采纳（A/C/D 为 09-13 建议名单内标的）</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交）</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M04</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>哈药股份</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>（600664）</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7.33</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>36650</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>人工采纳 09-13《明日买入建议》★核心2：候选池第 2 名；当日该股 +4.43%，成交价高于前收盘。</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>估值与盈利指标取东财快照/F10 口径（见 data/fin 与仪表盘标的明细）</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-14 收盘：现价7.3，MA20=8.34，MA60=6.22，RSI14=40.1，技术面评分63。</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3885.33(-0.07%)；深证成指 13384.57(-0.64%)；沪深300 4480.08(-0.67%)；科创50 1528.27(-1.62%)。09-14 为普跌日，本次买入为逆势加仓。</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>本批 5 笔合计 66.21 万元，使组合现金占比由 21.78% 降至约 8.28%，跌破策略现金下限 20%；且买入当日为普跌日，属逆势加仓，须严格执行个股止损纪律（-8% 或跌破 MA20）。</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：RED；交易后现金占比8%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>是（09-13 DeepSeek 收盘复盘 + 09-13《明日买入建议》全市场筛选）</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>采纳（A/C/D 为 09-13 建议名单内标的）</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交）</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M05</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>深信服</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>（300454）</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>136.73</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>68365</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>人工主动建仓（不在 09-13 建议名单内）：深信服属当日 +4.96% 的网络安全/云计算方向，人工判断动量延续。</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>估值与盈利指标取东财快照/F10 口径（见 data/fin 与仪表盘标的明细）</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-14 收盘：现价134.26，MA20=126.08，MA60=114.30，RSI14=67.4，技术面评分60。</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3885.33(-0.07%)；深证成指 13384.57(-0.64%)；沪深300 4480.08(-0.67%)；科创50 1528.27(-1.62%)。09-14 为普跌日，本次买入为逆势加仓。</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>本批 5 笔合计 66.21 万元，使组合现金占比由 21.78% 降至约 8.28%，跌破策略现金下限 20%；且买入当日为普跌日，属逆势加仓，须严格执行个股止损纪律（-8% 或跌破 MA20）。</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：RED；交易后现金占比8%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>是（09-13 DeepSeek 收盘复盘 + 09-13《明日买入建议》全市场筛选）</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>部分采纳（标的不在建议名单内，属人工主动决策）</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交）</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M06</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>（601899）</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>32.25</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>225750</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>人工执行调仓单（采纳AI修正意见）：09-14 跌破20日线，但仍在60日线上方且基本面优秀（ROE19.6%、净利+68%），故只减至约12.7%保留核心仓位，不全清。</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>减仓依据为价格/风控纪律与组合现金约束，非基本面恶化</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-14 收盘：现价32.25，MA20=33.64，MA60=30.99，RSI14=40.3，技术面评分56。</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3885.33(-0.07%)；深证成指 13384.57(-0.64%)；沪深300 4480.08(-0.67%)；科创50 1528.27(-1.62%)。09-14 买入 5 笔后现金降至 8.3%，本次减仓为现金纪律纠偏，计划 09-15 开盘执行。</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>减仓后紫金权重约12.7%，仍为主要风险敞口，须跌破前低（31.5附近）继续减。</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>是（09-14 DeepSeek 收盘复盘 + 系统现金下限约束）</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>采纳（含 AI 对紫金'只减至约12%、沪深300ETF不卖'的修正意见）</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策；计划 2026-09-15 开盘执行，成交价待回填实际值）</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M07</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>星网锐捷</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>（002396）</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>34.82</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>3900</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>135798</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>人工执行调仓单：09-14 当日建仓即跌破20日线，按纪律减未确认部分。</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>减仓依据为价格/风控纪律与组合现金约束，非基本面恶化</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-14 收盘：现价34.82，MA20=35.11，MA60=29.75，RSI14=60.3，技术面评分56。</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3885.33(-0.07%)；深证成指 13384.57(-0.64%)；沪深300 4480.08(-0.67%)；科创50 1528.27(-1.62%)。09-14 买入 5 笔后现金降至 8.3%，本次减仓为现金纪律纠偏，计划 09-15 开盘执行。</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>建仓当日即破位属追高，剩余6,100股须严格执行止损。</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>是（09-14 DeepSeek 收盘复盘 + 系统现金下限约束）</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>采纳（含 AI 对紫金'只减至约12%、沪深300ETF不卖'的修正意见）</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策；计划 2026-09-15 开盘执行，成交价待回填实际值）</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M08</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>新集能源</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>（601918）</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>10.32</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>9500</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>98040</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>人工执行调仓单：跌破20日线且不在候选池内的非策略标的，减半保留观察仓。</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>减仓依据为价格/风控纪律与组合现金约束，非基本面恶化</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-14 收盘：现价10.32，MA20=10.48，MA60=9.83，RSI14=46.6，技术面评分56。</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3885.33(-0.07%)；深证成指 13384.57(-0.64%)；沪深300 4480.08(-0.67%)；科创50 1528.27(-1.62%)。09-14 买入 5 笔后现金降至 8.3%，本次减仓为现金纪律纠偏，计划 09-15 开盘执行。</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>该股不在观察池与候选池内，属人工主动持仓，注意流动性。</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>是（09-14 DeepSeek 收盘复盘 + 系统现金下限约束）</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>采纳（含 AI 对紫金'只减至约12%、沪深300ETF不卖'的修正意见）</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策；计划 2026-09-15 开盘执行，成交价待回填实际值）</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M09</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>恺英网络</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>（002517）</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>17.01</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>85050</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>人工执行调仓单：跌破20日线，且 AI 09-14 复核意见亦点名应减该标的。</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>减仓依据为价格/风控纪律与组合现金约束，非基本面恶化</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-14 收盘：现价17.01，MA20=17.02，MA60=16.82，RSI14=55.6，技术面评分62。</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3885.33(-0.07%)；深证成指 13384.57(-0.64%)；沪深300 4480.08(-0.67%)；科创50 1528.27(-1.62%)。09-14 买入 5 笔后现金降至 8.3%，本次减仓为现金纪律纠偏，计划 09-15 开盘执行。</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>游戏板块情绪波动大，减半后剩余仓位仍暴露于板块回调。</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>是（09-14 DeepSeek 收盘复盘 + 系统现金下限约束）</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>采纳（含 AI 对紫金'只减至约12%、沪深300ETF不卖'的修正意见）</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策；计划 2026-09-15 开盘执行，成交价待回填实际值）</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M10</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>招商轮船</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>（601872）</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>人工执行调仓单：09-14 当日建仓后即跌破成本，先减半（该股为AI建议的欠配标的，回到20日线上方可补回）。</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>减仓依据为价格/风控纪律与组合现金约束，非基本面恶化</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-14 收盘：现价20.0，MA20=19.07，MA60=17.52，RSI14=57.7，技术面评分67。</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3885.33(-0.07%)；深证成指 13384.57(-0.64%)；沪深300 4480.08(-0.67%)；科创50 1528.27(-1.62%)。09-14 买入 5 笔后现金降至 8.3%，本次减仓为现金纪律纠偏，计划 09-15 开盘执行。</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>仓位极小（0.2%），减半影响有限，主要作用是止损纪律留痕。</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>是（09-14 DeepSeek 收盘复盘 + 系统现金下限约束）</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>采纳（含 AI 对紫金'只减至约12%、沪深300ETF不卖'的修正意见）</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策；计划 2026-09-15 开盘执行，成交价待回填实际值）</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2976,6 +2976,96 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M11</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>药明康德</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>（603259）</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>157.70</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>157700</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>人工采纳 09-14 AI 推荐（DeepSeek 收盘复盘给出'买入 药明康德 155~162、止损146、目标185、盈亏比2.12、建议仓位8%'，为该次推荐信心最高的一只；CXO板块当日领涨+5.75%）。</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>PE(TTM)22.2，ROE13.2%、营收同比+39%，CXO 龙头，估值与增速匹配。</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>截至 09-14 收盘：现价158.86，MA20=157.67，MA60=139.63，RSI14=47.2，技术面评分60。</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3885.33(-0.07%)；深证成指 13384.57(-0.64%)；沪深300 4480.08(-0.67%)；科创50 1528.27(-1.62%)（09-14 收盘，09-15 盘中执行交易）。</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>CXO 板块情绪与海外订单/政策扰动；本笔买入后现金占比降至约16.5%，低于策略下限20%（超限）。</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：RED；交易后现金占比16%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>是（09-14 DeepSeek 收盘复盘推荐买入）</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交 2026-09-15）</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>人工执行调仓单（采纳AI修正意见）：09-14 跌破20日线，但仍在60日线上方且基本面优秀（ROE19.6%、净利+68%），故只减至约12.7%保留核心仓位，不全清。</t>
+          <t>人工执行调仓单（采纳AI修正意见）：09-14 跌破20日线，但仍在60日线上方且基本面优秀（ROE19.6%、净利+68%），故只减至约12.7%保留核心仓位，不全清。（注：本笔 09-15 实际未成交，仅留审计痕迹）</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED（人工主动决策；计划 2026-09-15 开盘执行，成交价待回填实际值）</t>
+          <t>VOID（该笔 09-15 委托未成交，已于 09-16 二次手动卖出，见 D20260916M04）</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -3061,6 +3061,276 @@
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>D20260916M02</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>赤峰黄金</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>（600988）</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>43.56</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>392040</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>人工主动建仓：赤峰黄金为 09-13 建议名单核心3（贵金属），近期回调后人工判断黄金板块配置价值。</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>贵金属板块，受益金价；09-13 建议时 PE22.8、净利同比+56.5%</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>截至 09-15 收盘：现价43.54，MA20=45.95，MA60=38.69，RSI14=34.5，技术面评分61；09-16 盘中现价 45.26（+3.95%）。</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3864.28(-0.54%)；深证成指 13287.97(-0.72%)；沪深300 4450.04(-0.67%)；科创50 1551.96(+1.55%)（09-15 收盘口径，09-16 盘中执行）。</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>金价回落与板块高位波动；本笔买入后现金进一步下降，需注意仓位纪律。</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>是（09-14 DeepSeek 分析与 09-13/09-14《明日买入建议》）</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>采纳（09-13《明日买入建议》名单内标的）</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交 2026-09-16）</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>D20260916M03</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康龙化成</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>（300759）</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>42650</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>人工主动建仓：康龙化成属 CXO 链条，09-14 AI 市场解读指出医疗研发外包板块资金集中（+5.75%），人工跟随板块动量。</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>CXO/医疗服务，PE45.8、医药研发外包景气度回升</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>截至 09-15 收盘：现价42.36，MA20=43.82，MA60=39.39，RSI14=43.2，技术面评分63；09-16 盘中现价 42.93（+1.35%）。</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3864.28(-0.54%)；深证成指 13287.97(-0.72%)；沪深300 4450.04(-0.67%)；科创50 1551.96(+1.55%)（09-15 收盘口径，09-16 盘中执行）。</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>估值偏高、板块情绪波动大；仓位较小（约0.9%）</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>是（09-14 DeepSeek 分析与 09-13/09-14《明日买入建议》）</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>部分采纳（09-14 AI 提及 CXO 方向，但未直接推荐该标的）</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交 2026-09-16）</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>D20260916M04</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>（601899）</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>31.53</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>441420</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>人工执行减仓：09-15 的委托未成交，09-16 二次手动卖出。紫金浮亏且跌破20日线，减持以修复现金纪律并把最大单一风险敞口降下来。</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>紫金基本面仍为候选池第一（综合78、基本面100），本次减持属风控与现金约束，非基本面恶化</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>截至 09-15 收盘：现价31.68，MA20=33.56，MA60=31.06，RSI14=30.4，技术面评分61。</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3864.28(-0.54%)；深证成指 13287.97(-0.72%)；沪深300 4450.04(-0.67%)；科创50 1551.96(+1.55%)（09-15 收盘口径，09-16 盘中执行）。</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>减持后保留 12,300 股（约8.0%）；若跌破 MA60 或触及 -8% 止损须继续减</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>是（09-14 DeepSeek 分析、09-13《明日买入建议》）</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>采纳（09-16 操作建议的减仓方向，股数按实际成交 14,000）</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交 2026-09-16）</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3287,27 +3287,27 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>人工执行减仓：09-15 的委托未成交，09-16 二次手动卖出。紫金浮亏且跌破20日线，减持以修复现金纪律并把最大单一风险敞口降下来。</t>
+          <t>人工执行减仓（09-16 实际成交）</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>紫金基本面仍为候选池第一（综合78、基本面100），本次减持属风控与现金约束，非基本面恶化</t>
+          <t>风控与现金约束</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>截至 09-15 收盘：现价31.68，MA20=33.56，MA60=31.06，RSI14=30.4，技术面评分61。</t>
+          <t>见当日记录</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>上证指数 3864.28(-0.54%)；深证成指 13287.97(-0.72%)；沪深300 4450.04(-0.67%)；科创50 1551.96(+1.55%)（09-15 收盘口径，09-16 盘中执行）。</t>
+          <t>09-15 收盘口径</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>减持后保留 12,300 股（约8.0%）；若跌破 MA60 或触及 -8% 止损须继续减</t>
+          <t>保留底仓，跌破MA60继续减</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>是（09-14 DeepSeek 分析、09-13《明日买入建议》）</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>采纳（09-16 操作建议的减仓方向，股数按实际成交 14,000）</t>
+          <t>采纳</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3331,6 +3331,366 @@
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>D2026091701</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>（601899）</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>30.90</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>6300</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>194670</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>止损触发：浮亏-8.9% ≤ 止损线-8%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>基本面/价格双重纪律</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>浮盈-8.9%触发价格纪律</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4460.16点（-0.45%），跌破20日均线；两市成交额约18231亿元，较前5日均量放大（前5日均值约17400亿元），市场活跃度提升。；机会：当日领涨板块为种子、视频媒体、房产租赁经纪，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>锁定收益/防止进一步亏损，执行交易纪律</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：YELLOW；交易后现金占比28%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>D20260917M01</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>（601318）</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>53.54</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>160620</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>人工执行减仓以修复现金纪律（现金 11.97% 低于下限 20%）；减持跌破20日线的弱势大仓位，采纳 AI 与系统调仓单方向，股数按实际成交。</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>减仓依据为价格纪律与组合现金约束，非基本面恶化</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-16 收盘：现价53.51，MA20=54.77，MA60=52.09，RSI14=42.4，技术面评分56。</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3891.60(+0.71%)；深证成指 13454.74(+1.26%)；沪深300 4480.27(+0.68%)；科创50 1616.19(+4.14%)（09-16 收盘）。</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>减持后仍保留底仓；若继续跌破 MA60 或触及 -8% 止损，剩余部分按纪律处理。</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>是（09-16 DeepSeek 收盘复盘调仓复核意见 + 系统现金下限约束）</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>采纳（方向一致；AI 原建议减平安10,600股，实际按人工判断减3,000股并同步减持赤峰/紫金）</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交 2026-09-17）</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>D20260917M02</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>赤峰黄金</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>（600988）</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>42.74</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>213700</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>人工执行减仓以修复现金纪律（现金 11.97% 低于下限 20%）；减持跌破20日线的弱势大仓位，采纳 AI 与系统调仓单方向，股数按实际成交。</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>减仓依据为价格纪律与组合现金约束，非基本面恶化</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-16 收盘：现价45.44，MA20=46.09，MA60=38.98，RSI14=37.6，技术面评分60。</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3891.60(+0.71%)；深证成指 13454.74(+1.26%)；沪深300 4480.27(+0.68%)；科创50 1616.19(+4.14%)（09-16 收盘）。</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>减持后仍保留底仓；若继续跌破 MA60 或触及 -8% 止损，剩余部分按纪律处理。</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>是（09-16 DeepSeek 收盘复盘调仓复核意见 + 系统现金下限约束）</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>采纳（方向一致；AI 原建议减平安10,600股，实际按人工判断减3,000股并同步减持赤峰/紫金）</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交 2026-09-17）</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>D20260917M03</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>（601899）</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>30.66</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>183960</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>人工执行减仓以修复现金纪律（现金 11.97% 低于下限 20%）；减持跌破20日线的弱势大仓位，采纳 AI 与系统调仓单方向，股数按实际成交。</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>减仓依据为价格纪律与组合现金约束，非基本面恶化</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>截至 2026-09-16 收盘：现价32.17，MA20=33.55，MA60=31.15，RSI14=34.0，技术面评分65。</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3891.60(+0.71%)；深证成指 13454.74(+1.26%)；沪深300 4480.27(+0.68%)；科创50 1616.19(+4.14%)（09-16 收盘）。</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>减持后仍保留底仓；若继续跌破 MA60 或触及 -8% 止损，剩余部分按纪律处理。</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>是（09-16 DeepSeek 收盘复盘调仓复核意见 + 系统现金下限约束）</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>采纳（方向一致；AI 原建议减平安10,600股，实际按人工判断减3,000股并同步减持赤峰/紫金）</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交 2026-09-17）</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3696,6 +3696,96 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>D2026091801</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>（601899）</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>31.41</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>11800</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>370638</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>综合评分80.0分（基本面100/技术面60.0）达标，目标仓位24%，买入后占比7.7%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好；归母净利润同比+68.17%，利润端表现强劲</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>中期趋势向上，可关注/持有。指标信号：价格站上60日均线；MACD红柱放大；RSI=36.3中性区</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4507.39点（+1.06%），跌破20日均线；两市成交额约20771亿元，较前5日均量放大（前5日均值约17752亿元），市场活跃度提升。；机会：当日领涨板块为其他医疗服务、房产租赁经纪、半导体设备，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比20%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3728,16 +3728,16 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>11800</v>
+        <v>10300</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>370638</t>
+          <t>323523</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>综合评分80.0分（基本面100/技术面60.0）达标，目标仓位24%，买入后占比7.7%</t>
+          <t>综合评分80.0分（基本面100/技术面60.0）达标，目标仓位24%，买入后占比6.7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3782,7 +3782,97 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>D20260918M01</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>药明康德</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>（603259）</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>159.35</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>47805</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>人工采纳 09-18 操作建议：药明康德为 AI 与程序榜单双重推荐标的，现价刚站上 MA20、权重欠配，按建议买 300 股。</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>PE(TTM) 约22，ROE13.2%、营收同比+39%，CXO 龙头，估值与增速匹配</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>截至 09-17 收盘：现价160.49，MA20=156.54，MA60=141.92，RSI14=56.0，技术面评分60。</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>上证指数 3875.60(-0.41%)；深证成指 13409.91(-0.33%)；沪深300 4460.16(-0.45%)；科创50 1606.29(-0.61%)（09-17 收盘口径）。</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>CXO 板块情绪与海外政策扰动；本笔金额小（4.8万），对现金纪律影响有限。</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>是（09-16 DeepSeek 收盘复盘推荐'买入药明康德 154~160、目标180、仓位8%'）</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED（人工主动决策，已于同花顺模拟盘实际成交 2026-09-18）</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
         </is>
       </c>
     </row>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3876,6 +3876,96 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>D2026092801</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪深300ETF</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>（510300）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>258900</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>1143561</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>技术面恶化：MACD死叉且技术评分37分</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>基本面/价格双重纪律</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD死叉；RSI=26.4超卖区</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4340.76点（-2.22%），跌破20日均线；两市成交额约17028亿元，较前5日均量萎缩（前5日均值约19325亿元），市场情绪偏谨慎。；机会：当日领涨板块为林业Ⅲ、林业Ⅱ、其他医疗服务，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>锁定收益/防止进一步亏损，执行交易纪律</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比44%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3966,6 +3966,186 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>D2026092901</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>（601899）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>29.55</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>28300</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>836265</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>综合评分77.0分（基本面100/技术面54.0）达标，目标仓位24%，买入后占比24.0%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好；归母净利润同比+68.17%，利润端表现强劲</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>趋势中性，观望。指标信号：价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=22.6超卖区；近20日已跌-12.2%，接近超跌</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4352.79点（+0.28%），跌破20日均线；两市成交额约11564亿元，较前5日均量萎缩（前5日均值约18576亿元），市场情绪偏谨慎。；机会：当日领涨板块为林业Ⅲ、林业Ⅱ、其他医疗服务，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比27%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>D2026092902</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>（300750）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>286.80</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>315480</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>综合评分70.5分（基本面87.0/技术面54.0）达标，目标仓位24%，买入后占比6.6%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好；归母净利润同比+41.98%，利润端表现强劲</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>趋势中性，观望。指标信号：价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.3超卖区；近20日已跌-21.1%，接近超跌</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4352.79点（+0.28%），跌破20日均线；两市成交额约11564亿元，较前5日均量萎缩（前5日均值约18576亿元），市场情绪偏谨慎。；机会：当日领涨板块为林业Ⅲ、林业Ⅱ、其他医疗服务，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比38%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4146,6 +4146,96 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>D2026101401</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>（601318）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>51.23</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>18200</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>932386</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>止损触发：浮亏-8.7% ≤ 止损线-8%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>基本面/价格双重纪律</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>浮盈-8.7%触发价格纪律</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4217.68点（-1.36%），跌破20日均线；两市成交额约14144亿元，较前5日均量萎缩（前5日均值约16469亿元），市场情绪偏谨慎。；机会：当日领涨板块为其他数字媒体、印制电路板、纺织化学制品，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>锁定收益/防止进一步亏损，执行交易纪律</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：YELLOW；交易后现金占比40%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4236,6 +4236,96 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>D2026101501</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>长江电力</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>（600900）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>29.60</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>858400</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>综合评分72.0分（基本面78.0/技术面66.0）达标，目标仓位24%，买入后占比24.0%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长；归母净利润同比+13.02%，利润端表现强劲</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>中期趋势向上，可关注/持有。指标信号：均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=70.2中性区</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4166.01点（-1.23%），跌破20日均线；两市成交额约16330亿元，较前5日均量萎缩（前5日均值约16422亿元），市场情绪偏谨慎。；机会：当日领涨板块为卫浴电器、纺织鞋类制造、大众出版，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比22%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4326,6 +4326,96 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>D2026101901</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>（300750）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>267.02</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>293722</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>移动止损触发：自持仓最高价306.71回撤12.9% ≥ 12%（当前浮盈-6.9%）</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>持有期内基本面未见恶化，触发为价格纪律</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>浮盈-6.9%触发价格纪律</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4174.53点（+0.09%），跌破20日均线；两市成交额约14375亿元，较前5日均量萎缩（前5日均值约15633亿元），市场情绪偏谨慎。；机会：当日领涨板块为其他数字媒体、地面兵装Ⅲ、地面兵装Ⅱ，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>锁定收益/防止进一步亏损，执行交易纪律</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比28%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R44"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4416,6 +4416,96 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>D2026102001</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>美的集团</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>（000333）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>85.28</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>383760</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>综合评分67.5分（基本面75.0/技术面60.0）达标，目标仓位24%，买入后占比8.2%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长；归母净利润同比+1.66%，利润平稳</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>中期趋势向上，可关注/持有。指标信号：价格站上60日均线；MACD红柱放大；RSI=61.3中性区</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4152.11点（-0.54%），跌破20日均线；两市成交额约14561亿元，较前5日均量萎缩（前5日均值约15433亿元），市场情绪偏谨慎。；机会：当日领涨板块为其他数字媒体、地面兵装Ⅲ、地面兵装Ⅱ，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比20%</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4506,6 +4506,96 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>D2026102201</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>（601899）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>27.84</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>38600</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>1074624</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>移动止损触发：自持仓最高价31.77回撤12.4% ≥ 12%（当前浮盈-7.3%）</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>持有期内基本面未见恶化，触发为价格纪律</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>浮盈-7.3%触发价格纪律</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4036.30点（-1.84%），跌破20日均线；两市成交额约15287亿元，较前5日均量放大（前5日均值约15023亿元），市场活跃度提升。；机会：当日领涨板块为电机Ⅲ、电机Ⅱ、医美耗材，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>锁定收益/防止进一步亏损，执行交易纪律</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比43%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/07_投资决策记录.xlsx
+++ b/outputs/07_投资决策记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4596,6 +4596,96 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>D2026102301</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>（300750）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>237.60</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>1069200</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>综合评分76.5分（基本面94.0/技术面59.0）达标，目标仓位24%，买入后占比23.0%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>加权ROE=17.64%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+56.19%，成长性较好；归母净利润同比+31.60%，利润端表现强劲</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>趋势中性，观望。指标信号：价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=27.5超卖区；5日均量为60日均量的2.39倍，量能放大；近20日已跌-21.9%，接近超跌</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4105.33点（+1.71%），跌破20日均线；两市成交额约19563亿元，较前5日均量放大（前5日均值约14814亿元），市场活跃度提升。；机会：当日领涨板块为其他数字媒体、机器人、视频媒体，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>规则引擎：GREEN；交易后现金占比20%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>是（数据采集、指标计算与评分由自动化分析流水线完成）</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>采纳系统评分，价格与数量按预设策略确定</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>PENDING（待人工确认：按预设策略自动生成，可在同花顺下单执行后于 confirmations.csv 确认）</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
